--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://confiascs-my.sharepoint.com/personal/bporras_confia_co_cr/Documents/Documentos/UiPath/RPA_Respaldos_Backup/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://confiascs-my.sharepoint.com/personal/bporras_confia_co_cr/Documents/Documentos/UiPath/RPA_CNF_Respaldos_D21/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{5FA6F838-CDF2-4CD6-A39F-51CB33E2959B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{938E58C3-6BDB-481F-A5DB-AEEE2C5CF417}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{5FA6F838-CDF2-4CD6-A39F-51CB33E2959B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3C023A9-EBF5-4145-9A43-3678EFDB19AA}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1500" yWindow="1104" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="82">
   <si>
     <t>Name</t>
   </si>
@@ -203,9 +203,6 @@
     <t>Screenshots_Path</t>
   </si>
   <si>
-    <t>C:\Users\rpa\Documents\Screenshots</t>
-  </si>
-  <si>
     <t>AWS_AccountID</t>
   </si>
   <si>
@@ -230,9 +227,6 @@
     <t>TransactionType</t>
   </si>
   <si>
-    <t>DIFERENCIAL_12</t>
-  </si>
-  <si>
     <t>Email_From</t>
   </si>
   <si>
@@ -264,6 +258,18 @@
   </si>
   <si>
     <t>RPA_Respaldos_Queue</t>
+  </si>
+  <si>
+    <t>C:\Users\rpa\Documents\Screenshots\RPA_Respaldos</t>
+  </si>
+  <si>
+    <t>DIFERENCIAL_21</t>
+  </si>
+  <si>
+    <t>TemplatePath</t>
+  </si>
+  <si>
+    <t>Data\Templates\EmailRespaldos.txt</t>
   </si>
 </sst>
 </file>
@@ -370,7 +376,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -387,7 +393,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -684,7 +690,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z996"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.5546875" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
@@ -731,7 +737,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C2" s="2"/>
     </row>
@@ -740,11 +746,11 @@
         <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C3" s="4"/>
     </row>
-    <row r="4" spans="1:26" ht="34.200000000000003" customHeight="1">
+    <row r="4" spans="1:26" ht="28.8">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -789,7 +795,7 @@
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" s="9">
         <v>969121359235</v>
@@ -800,7 +806,7 @@
         <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
@@ -853,53 +859,60 @@
     </row>
     <row r="17" spans="1:2" ht="14.25" customHeight="1">
       <c r="A17" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" t="s">
         <v>63</v>
-      </c>
-      <c r="B17" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.25" customHeight="1">
       <c r="A18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" t="s">
         <v>65</v>
-      </c>
-      <c r="B18" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.25" customHeight="1">
       <c r="A19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.25" customHeight="1">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="14.25" customHeight="1">
       <c r="A21" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="14.25" customHeight="1">
       <c r="A22" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="14.25" customHeight="1"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A23" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" t="s">
+        <v>81</v>
+      </c>
+    </row>
     <row r="24" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="25" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="26" spans="1:2" ht="14.25" customHeight="1"/>
@@ -1887,7 +1900,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z988"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
     <col min="2" max="2" width="51" customWidth="1"/>
@@ -3045,7 +3058,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C998"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.88671875" customWidth="1"/>
     <col min="2" max="2" width="30.109375" customWidth="1"/>
@@ -3058,32 +3071,32 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="14.25" customHeight="1">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14.25" customHeight="1">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="14.25" customHeight="1">
